--- a/uploads/M3M CALLING DATA 380-761.xlsx
+++ b/uploads/M3M CALLING DATA 380-761.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="1009">
   <si>
     <t>7022620659</t>
   </si>
@@ -3039,6 +3039,31 @@
   </si>
   <si>
     <t>MH TW-05-2604, M3M Heights, Sector-65, Gurugram , 122001,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>NOT AVAILABEL</t>
+  </si>
+  <si>
+    <t>INCOMING CALL NOT AVAILABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH TW-04-1703, M3M Heights, Sector-65, Gurugram , 4, 122001, </t>
+  </si>
+  <si>
+    <t>NOT AVAILABLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH TW-04-2503, M3M Heights, Sector-65, Gurugram , 4, 122001, </t>
+  </si>
+  <si>
+    <t>MH TW-04-2704, M3M Heights, Sector-65, Gurugram , 4, 122001,</t>
   </si>
 </sst>
 </file>
@@ -4965,7 +4990,7 @@
         <v>1021</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>207</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -4973,7 +4998,7 @@
         <v>760</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>759</v>
+        <v>1005</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>758</v>
@@ -5220,7 +5245,7 @@
         <v>1021</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>207</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5322,7 +5347,7 @@
         <v>1021</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>994</v>
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5441,7 +5466,7 @@
         <v>1021</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>543</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6934,7 +6959,9 @@
       <c r="D203" s="2">
         <v>1147</v>
       </c>
-      <c r="E203" s="1"/>
+      <c r="E203" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="204" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
@@ -7130,7 +7157,9 @@
       <c r="D215" s="2">
         <v>1109</v>
       </c>
-      <c r="E215" s="1"/>
+      <c r="E215" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="216" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
@@ -7145,7 +7174,9 @@
       <c r="D216" s="2">
         <v>1147</v>
       </c>
-      <c r="E216" s="1"/>
+      <c r="E216" s="1" t="s">
+        <v>1006</v>
+      </c>
     </row>
     <row r="217" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
@@ -7178,7 +7209,7 @@
         <v>1021</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>409</v>
+        <v>543</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7186,7 +7217,7 @@
         <v>408</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>407</v>
+        <v>1007</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>404</v>
@@ -7194,7 +7225,9 @@
       <c r="D219" s="2">
         <v>1147</v>
       </c>
-      <c r="E219" s="1"/>
+      <c r="E219" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="220" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
@@ -7258,7 +7291,9 @@
       <c r="D223" s="2">
         <v>1147</v>
       </c>
-      <c r="E223" s="1"/>
+      <c r="E223" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="224" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
@@ -7273,7 +7308,9 @@
       <c r="D224" s="2">
         <v>1147</v>
       </c>
-      <c r="E224" s="1"/>
+      <c r="E224" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="225" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
@@ -7322,14 +7359,16 @@
       <c r="D227" s="2">
         <v>1147</v>
       </c>
-      <c r="E227" s="1"/>
+      <c r="E227" s="1" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="228" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>384</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>383</v>
+        <v>1008</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>382</v>
@@ -7337,7 +7376,9 @@
       <c r="D228" s="2">
         <v>1147</v>
       </c>
-      <c r="E228" s="1"/>
+      <c r="E228" s="1" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="229" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
@@ -7370,7 +7411,7 @@
         <v>780</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>207</v>
+        <v>543</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7386,7 +7427,9 @@
       <c r="D231" s="2">
         <v>1147</v>
       </c>
-      <c r="E231" s="1"/>
+      <c r="E231" s="1" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="232" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
@@ -7401,7 +7444,9 @@
       <c r="D232" s="2">
         <v>1109</v>
       </c>
-      <c r="E232" s="1"/>
+      <c r="E232" s="1" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="233" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
@@ -7433,7 +7478,9 @@
       <c r="D234" s="2">
         <v>1021</v>
       </c>
-      <c r="E234" s="1"/>
+      <c r="E234" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="235" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
@@ -7448,7 +7495,9 @@
       <c r="D235" s="2">
         <v>1147</v>
       </c>
-      <c r="E235" s="1"/>
+      <c r="E235" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="236" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
@@ -7463,7 +7512,9 @@
       <c r="D236" s="2">
         <v>1147</v>
       </c>
-      <c r="E236" s="1"/>
+      <c r="E236" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="237" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
@@ -7478,7 +7529,9 @@
       <c r="D237" s="2">
         <v>1021</v>
       </c>
-      <c r="E237" s="1"/>
+      <c r="E237" s="1" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="238" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
@@ -7493,7 +7546,9 @@
       <c r="D238" s="2">
         <v>1021</v>
       </c>
-      <c r="E238" s="1"/>
+      <c r="E238" s="1" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="239" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
@@ -7508,7 +7563,9 @@
       <c r="D239" s="2">
         <v>1147</v>
       </c>
-      <c r="E239" s="1"/>
+      <c r="E239" s="1" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="240" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
@@ -7523,7 +7580,9 @@
       <c r="D240" s="2">
         <v>1147</v>
       </c>
-      <c r="E240" s="1"/>
+      <c r="E240" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="241" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
@@ -7538,7 +7597,9 @@
       <c r="D241" s="2">
         <v>1021</v>
       </c>
-      <c r="E241" s="1"/>
+      <c r="E241" s="1" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="242" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
@@ -7553,7 +7614,9 @@
       <c r="D242" s="2">
         <v>1021</v>
       </c>
-      <c r="E242" s="1"/>
+      <c r="E242" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="243" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
@@ -7568,7 +7631,9 @@
       <c r="D243" s="2">
         <v>1147</v>
       </c>
-      <c r="E243" s="1"/>
+      <c r="E243" s="1" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="244" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">

--- a/uploads/M3M CALLING DATA 380-761.xlsx
+++ b/uploads/M3M CALLING DATA 380-761.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="1018">
   <si>
     <t>7022620659</t>
   </si>
@@ -3064,6 +3064,33 @@
   </si>
   <si>
     <t>MH TW-04-2704, M3M Heights, Sector-65, Gurugram , 4, 122001,</t>
+  </si>
+  <si>
+    <t>21000/-UNIT NUMBET-3404</t>
+  </si>
+  <si>
+    <t>MH TW-04-1904, M3M Heights, Sector-65, Gurugram , 4, 122001,</t>
+  </si>
+  <si>
+    <t>DUPLICATE N</t>
+  </si>
+  <si>
+    <t>DUPLICATE NUMB</t>
+  </si>
+  <si>
+    <t>18800 SALE  </t>
+  </si>
+  <si>
+    <t>RENTED OUT]</t>
+  </si>
+  <si>
+    <t>MH TW-05-1904, M3M Heights, Sector-65, Gurugram , 122001,</t>
+  </si>
+  <si>
+    <t>MH TW-06-1301, 13F,M3M Heights, Sector-65, Gurugram , 122001,</t>
+  </si>
+  <si>
+    <t>MH TW-05-2003, M3M Heights, Sector-65, Gurugram , 122001,</t>
   </si>
 </sst>
 </file>
@@ -3948,7 +3975,7 @@
         <v>919</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>918</v>
+        <v>1016</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>917</v>
@@ -4735,7 +4762,7 @@
         <v>1021</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -4803,7 +4830,7 @@
         <v>1147</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -4854,7 +4881,7 @@
         <v>1083</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -4905,7 +4932,7 @@
         <v>1021</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>203</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5007,7 +5034,7 @@
         <v>1109</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5024,7 +5051,7 @@
         <v>1083</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5032,7 +5059,7 @@
         <v>755</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>754</v>
+        <v>1015</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>753</v>
@@ -5041,7 +5068,7 @@
         <v>1147</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>207</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5058,7 +5085,7 @@
         <v>1109</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5092,7 +5119,7 @@
         <v>1021</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>207</v>
+        <v>539</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5109,7 +5136,7 @@
         <v>766</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5126,7 +5153,7 @@
         <v>1147</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>207</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5134,7 +5161,7 @@
         <v>738</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>737</v>
+        <v>1017</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>736</v>
@@ -5143,7 +5170,7 @@
         <v>1083</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5279,7 +5306,7 @@
         <v>1083</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>717</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5287,7 +5314,7 @@
         <v>716</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>715</v>
+        <v>1010</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>714</v>
@@ -5313,7 +5340,7 @@
         <v>1147</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>533</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5330,7 +5357,7 @@
         <v>1828</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5364,7 +5391,7 @@
         <v>1021</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5500,7 +5527,7 @@
         <v>1147</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5568,7 +5595,7 @@
         <v>1021</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>203</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5636,7 +5663,7 @@
         <v>1147</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5653,7 +5680,7 @@
         <v>1021</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>653</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5721,7 +5748,7 @@
         <v>1021</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5738,7 +5765,7 @@
         <v>766</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>365</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5755,7 +5782,7 @@
         <v>1083</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5840,7 +5867,7 @@
         <v>1147</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5891,7 +5918,7 @@
         <v>1109</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5976,7 +6003,7 @@
         <v>1021</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -5993,7 +6020,7 @@
         <v>766</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>539</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6010,7 +6037,7 @@
         <v>1083</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6044,7 +6071,7 @@
         <v>1021</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6061,7 +6088,7 @@
         <v>766</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6282,7 +6309,7 @@
         <v>1083</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6333,7 +6360,7 @@
         <v>766</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6350,7 +6377,7 @@
         <v>1083</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6367,7 +6394,7 @@
         <v>1147</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>539</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6384,7 +6411,7 @@
         <v>1021</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>994</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6418,7 +6445,7 @@
         <v>1083</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6503,7 +6530,7 @@
         <v>1147</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>194</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6571,7 +6598,7 @@
         <v>1109</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>194</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6588,7 +6615,7 @@
         <v>766</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>194</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6605,7 +6632,7 @@
         <v>1083</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6690,7 +6717,7 @@
         <v>1109</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -6843,7 +6870,7 @@
         <v>1828</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>194</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7158,7 +7185,7 @@
         <v>1109</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7175,7 +7202,7 @@
         <v>1147</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7192,7 +7219,7 @@
         <v>1021</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7258,7 +7285,7 @@
         <v>1021</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7326,7 +7353,7 @@
         <v>1021</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>203</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7411,7 +7438,7 @@
         <v>780</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7428,7 +7455,7 @@
         <v>1147</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7445,7 +7472,7 @@
         <v>1109</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7462,7 +7489,7 @@
         <v>1021</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>365</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="234" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7530,7 +7557,7 @@
         <v>1021</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>424</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7547,7 +7574,7 @@
         <v>1021</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7598,7 +7625,7 @@
         <v>1021</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>543</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7615,7 +7642,7 @@
         <v>1021</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>207</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -7648,7 +7675,9 @@
       <c r="D244" s="2">
         <v>1147</v>
       </c>
-      <c r="E244" s="1"/>
+      <c r="E244" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="245" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
@@ -7663,7 +7692,9 @@
       <c r="D245" s="2">
         <v>1021</v>
       </c>
-      <c r="E245" s="1"/>
+      <c r="E245" s="1" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="246" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
@@ -7678,7 +7709,9 @@
       <c r="D246" s="2">
         <v>1021</v>
       </c>
-      <c r="E246" s="1"/>
+      <c r="E246" s="1" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="247" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
@@ -7693,7 +7726,9 @@
       <c r="D247" s="2">
         <v>1147</v>
       </c>
-      <c r="E247" s="1"/>
+      <c r="E247" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="248" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
@@ -7708,7 +7743,9 @@
       <c r="D248" s="2">
         <v>1021</v>
       </c>
-      <c r="E248" s="1"/>
+      <c r="E248" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="249" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
@@ -7723,7 +7760,9 @@
       <c r="D249" s="2">
         <v>1021</v>
       </c>
-      <c r="E249" s="1"/>
+      <c r="E249" s="1" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="250" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
@@ -7738,7 +7777,9 @@
       <c r="D250" s="2">
         <v>1147</v>
       </c>
-      <c r="E250" s="1"/>
+      <c r="E250" s="1" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="251" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
@@ -7753,7 +7794,9 @@
       <c r="D251" s="2">
         <v>1109</v>
       </c>
-      <c r="E251" s="1"/>
+      <c r="E251" s="1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="252" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
@@ -7768,7 +7811,9 @@
       <c r="D252" s="2">
         <v>1021</v>
       </c>
-      <c r="E252" s="1"/>
+      <c r="E252" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="253" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
@@ -7783,7 +7828,9 @@
       <c r="D253" s="2">
         <v>1147</v>
       </c>
-      <c r="E253" s="1"/>
+      <c r="E253" s="1" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="254" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
@@ -7798,7 +7845,9 @@
       <c r="D254" s="2">
         <v>1147</v>
       </c>
-      <c r="E254" s="1"/>
+      <c r="E254" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="255" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
@@ -7813,7 +7862,9 @@
       <c r="D255" s="2">
         <v>1021</v>
       </c>
-      <c r="E255" s="1"/>
+      <c r="E255" s="1" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="256" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
@@ -7828,7 +7879,9 @@
       <c r="D256" s="2">
         <v>1021</v>
       </c>
-      <c r="E256" s="1"/>
+      <c r="E256" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="257" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
@@ -7843,7 +7896,9 @@
       <c r="D257" s="2">
         <v>1147</v>
       </c>
-      <c r="E257" s="1"/>
+      <c r="E257" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="258" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
@@ -7858,7 +7913,9 @@
       <c r="D258" s="2">
         <v>1147</v>
       </c>
-      <c r="E258" s="1"/>
+      <c r="E258" s="1" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="259" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
